--- a/output/pdf_financials_xlsx/MRVL.xlsx
+++ b/output/pdf_financials_xlsx/MRVL.xlsx
@@ -3474,7 +3474,7 @@
         </is>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.08080900000000001</v>
       </c>
       <c r="D92" s="3" t="n">
         <v>0.384442</v>
@@ -3489,10 +3489,10 @@
         <v>0.202137</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>0.294611</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>0.439673</v>
       </c>
     </row>
     <row r="93">
@@ -3806,13 +3806,13 @@
         <v>0</v>
       </c>
       <c r="D103" s="3" t="n">
-        <v>0</v>
+        <v>-0.035</v>
       </c>
       <c r="E103" s="3" t="n">
-        <v>0</v>
+        <v>-0.01575</v>
       </c>
       <c r="F103" s="3" t="n">
-        <v>0</v>
+        <v>-0.248146</v>
       </c>
       <c r="G103" s="3" t="n">
         <v>0.230043</v>
@@ -3899,13 +3899,13 @@
         <v>0.003076</v>
       </c>
       <c r="D106" s="3" t="n">
-        <v>0.103107</v>
+        <v>0.068107</v>
       </c>
       <c r="E106" s="3" t="n">
-        <v>-0.0756</v>
+        <v>-0.09135</v>
       </c>
       <c r="F106" s="3" t="n">
-        <v>0.605528</v>
+        <v>0.357382</v>
       </c>
       <c r="G106" s="3" t="n">
         <v>0.904515</v>
@@ -5536,7 +5536,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
           <t>-</t>
@@ -6034,7 +6038,11 @@
           <t>Prepaid and deposits 4</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>PrepaidAssets</t>
+        </is>
+      </c>
       <c r="E22" t="inlineStr">
         <is>
           <t>-</t>
@@ -6544,7 +6552,11 @@
           <t>Prepaid and deposits 5</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr"/>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>PrepaidAssets</t>
+        </is>
+      </c>
       <c r="E31" t="inlineStr">
         <is>
           <t>-</t>
@@ -7176,7 +7188,11 @@
           <t>Prepaid and deposits (notes 5 and 13)</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr"/>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>PrepaidAssets</t>
+        </is>
+      </c>
       <c r="E42" t="inlineStr">
         <is>
           <t>-</t>
@@ -8110,7 +8126,11 @@
           <t>Reserves (note 5)</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr"/>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E58" t="inlineStr">
         <is>
           <t>-</t>
@@ -11784,7 +11804,11 @@
           <t>Prepaids and deposits</t>
         </is>
       </c>
-      <c r="D123" t="inlineStr"/>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
       <c r="E123" t="inlineStr">
         <is>
           <t>-</t>
@@ -13082,7 +13106,11 @@
           <t>Prepaids and deposits 5</t>
         </is>
       </c>
-      <c r="D146" t="inlineStr"/>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
       <c r="E146" t="inlineStr">
         <is>
           <t>-</t>
@@ -14554,7 +14582,11 @@
           <t>Prepaid and deposits (note 5)</t>
         </is>
       </c>
-      <c r="D172" t="inlineStr"/>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
       <c r="E172" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/MRVL.xlsx
+++ b/output/pdf_financials_xlsx/MRVL.xlsx
@@ -759,16 +759,16 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.003439</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.002005</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.000403</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.000239</v>
       </c>
       <c r="F12" s="3" t="n">
         <v>0</v>
@@ -780,7 +780,7 @@
         <v>0</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>0.001934</v>
       </c>
     </row>
     <row r="13">
@@ -1294,16 +1294,16 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-0.010556</v>
+        <v>-0.013995</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.09804400000000001</v>
+        <v>-0.100049</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.955657</v>
+        <v>-0.95606</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-3.039346</v>
+        <v>-3.039585</v>
       </c>
       <c r="F27" s="3" t="n">
         <v>-2.554139</v>
@@ -1315,7 +1315,7 @@
         <v>-1.650079</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-2.211468</v>
+        <v>-2.213402</v>
       </c>
     </row>
     <row r="28">
@@ -1356,16 +1356,16 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.010556</v>
+        <v>-0.013995</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.09804400000000001</v>
+        <v>-0.100049</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.955244</v>
+        <v>-0.955647</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-3.039161</v>
+        <v>-3.0394</v>
       </c>
       <c r="F29" s="3" t="n">
         <v>-2.553987</v>
@@ -1377,7 +1377,7 @@
         <v>-1.650079</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-2.211468</v>
+        <v>-2.213402</v>
       </c>
     </row>
     <row r="30">
@@ -1527,22 +1527,22 @@
         <v>0.006232</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.22481</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>2.393144</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.593207</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.556622</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.345769</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.128855</v>
       </c>
     </row>
     <row r="35">
@@ -1593,22 +1593,22 @@
         <v>0.415232</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.22481</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>2.393144</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.593207</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.556622</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.345769</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.128855</v>
       </c>
     </row>
     <row r="37">
@@ -1989,22 +1989,22 @@
         <v>0.002004</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.29565</v>
+        <v>0.07084</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>2.468</v>
+        <v>0.07485600000000001</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.913541</v>
+        <v>0.320334</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.672389</v>
+        <v>0.115767</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.375386</v>
+        <v>0.029617</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.309166</v>
+        <v>0.180311</v>
       </c>
     </row>
     <row r="49">
@@ -4936,7 +4936,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -7132,7 +7132,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -16782,7 +16782,7 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
@@ -18886,7 +18886,7 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
@@ -20464,7 +20464,7 @@
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E276" s="5" t="n">

--- a/output/pdf_financials_xlsx/MRVL.xlsx
+++ b/output/pdf_financials_xlsx/MRVL.xlsx
@@ -1518,10 +1518,8 @@
           <t xml:space="preserve">    Cash and Cash Equivalents</t>
         </is>
       </c>
-      <c r="B34" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B34" s="3" t="n">
+        <v>0.007087</v>
       </c>
       <c r="C34" s="3" t="n">
         <v>0.006232</v>
@@ -1551,10 +1549,8 @@
           <t xml:space="preserve">    Marketable Securities</t>
         </is>
       </c>
-      <c r="B35" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B35" s="3" t="n">
+        <v>0.399</v>
       </c>
       <c r="C35" s="3" t="n">
         <v>0.409</v>
@@ -1584,10 +1580,8 @@
           <t xml:space="preserve">  Cash, Cash Equivalents, Marketable Securities</t>
         </is>
       </c>
-      <c r="B36" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B36" s="3" t="n">
+        <v>0.406087</v>
       </c>
       <c r="C36" s="3" t="n">
         <v>0.415232</v>
@@ -1617,10 +1611,8 @@
           <t xml:space="preserve">    Accounts Receivable</t>
         </is>
       </c>
-      <c r="B37" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B37" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C37" s="3" t="n">
         <v>0</v>
@@ -1650,10 +1642,8 @@
           <t xml:space="preserve">    Notes Receivable</t>
         </is>
       </c>
-      <c r="B38" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B38" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C38" s="3" t="n">
         <v>0</v>
@@ -1683,10 +1673,8 @@
           <t xml:space="preserve">    Loans Receivable</t>
         </is>
       </c>
-      <c r="B39" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B39" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C39" s="3" t="n">
         <v>0</v>
@@ -1716,10 +1704,8 @@
           <t xml:space="preserve">    Other Current Receivables</t>
         </is>
       </c>
-      <c r="B40" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B40" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C40" s="3" t="n">
         <v>0</v>
@@ -1749,10 +1735,8 @@
           <t xml:space="preserve">  Total Receivables</t>
         </is>
       </c>
-      <c r="B41" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B41" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C41" s="3" t="n">
         <v>0</v>
@@ -1782,10 +1766,8 @@
           <t xml:space="preserve">    Inventories, Raw Materials &amp; Components</t>
         </is>
       </c>
-      <c r="B42" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B42" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C42" s="3" t="n">
         <v>0</v>
@@ -1815,10 +1797,8 @@
           <t xml:space="preserve">    Inventories, Work In Process</t>
         </is>
       </c>
-      <c r="B43" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B43" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C43" s="3" t="n">
         <v>0</v>
@@ -1848,10 +1828,8 @@
           <t xml:space="preserve">    Inventories, Inventories Adjustments</t>
         </is>
       </c>
-      <c r="B44" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B44" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C44" s="3" t="n">
         <v>0</v>
@@ -1881,10 +1859,8 @@
           <t xml:space="preserve">    Inventories, Finished Goods</t>
         </is>
       </c>
-      <c r="B45" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B45" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C45" s="3" t="n">
         <v>0</v>
@@ -1914,10 +1890,8 @@
           <t xml:space="preserve">    Inventories, Other</t>
         </is>
       </c>
-      <c r="B46" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B46" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C46" s="3" t="n">
         <v>0</v>
@@ -1947,10 +1921,8 @@
           <t xml:space="preserve">  Total Inventories</t>
         </is>
       </c>
-      <c r="B47" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B47" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C47" s="3" t="n">
         <v>0</v>
@@ -1980,10 +1952,8 @@
           <t xml:space="preserve">  Other Current Assets</t>
         </is>
       </c>
-      <c r="B48" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B48" s="3" t="n">
+        <v>0.000553</v>
       </c>
       <c r="C48" s="3" t="n">
         <v>0.002004</v>
@@ -2013,10 +1983,8 @@
           <t xml:space="preserve">  Total Current Assets</t>
         </is>
       </c>
-      <c r="B49" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B49" s="3" t="n">
+        <v>0.40664</v>
       </c>
       <c r="C49" s="3" t="n">
         <v>0.417236</v>
@@ -2046,10 +2014,8 @@
           <t xml:space="preserve">  Investments And Advances</t>
         </is>
       </c>
-      <c r="B50" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B50" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C50" s="3" t="n">
         <v>0</v>
@@ -2079,10 +2045,8 @@
           <t xml:space="preserve">      Land And Improvements</t>
         </is>
       </c>
-      <c r="B51" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B51" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C51" s="3" t="n">
         <v>0</v>
@@ -2112,10 +2076,8 @@
           <t xml:space="preserve">      Buildings And Improvements</t>
         </is>
       </c>
-      <c r="B52" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B52" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C52" s="3" t="n">
         <v>0</v>
@@ -2145,10 +2107,8 @@
           <t xml:space="preserve">      Machinery, Furniture, Equipment</t>
         </is>
       </c>
-      <c r="B53" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B53" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C53" s="3" t="n">
         <v>0</v>
@@ -2178,10 +2138,8 @@
           <t xml:space="preserve">      Construction In Progress</t>
         </is>
       </c>
-      <c r="B54" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B54" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C54" s="3" t="n">
         <v>0</v>
@@ -2258,10 +2216,8 @@
           <t xml:space="preserve">    Gross Property, Plant and Equipment</t>
         </is>
       </c>
-      <c r="B56" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B56" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C56" s="3" t="n">
         <v>0</v>
@@ -2291,10 +2247,8 @@
           <t xml:space="preserve">    Accumulated Depreciation</t>
         </is>
       </c>
-      <c r="B57" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B57" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C57" s="3" t="n">
         <v>0</v>
@@ -2324,10 +2278,8 @@
           <t xml:space="preserve">  Property, Plant and Equipment</t>
         </is>
       </c>
-      <c r="B58" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B58" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C58" s="3" t="n">
         <v>0</v>
@@ -2357,10 +2309,8 @@
           <t xml:space="preserve">  Intangible Assets</t>
         </is>
       </c>
-      <c r="B59" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B59" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C59" s="3" t="n">
         <v>0</v>
@@ -2390,10 +2340,8 @@
           <t xml:space="preserve">    Goodwill</t>
         </is>
       </c>
-      <c r="B60" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B60" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C60" s="3" t="n">
         <v>0</v>
@@ -2423,10 +2371,8 @@
           <t xml:space="preserve">  Other Long Term Assets</t>
         </is>
       </c>
-      <c r="B61" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B61" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C61" s="3" t="n">
         <v>0</v>
@@ -2526,10 +2472,8 @@
           <t xml:space="preserve">    Accounts Payable</t>
         </is>
       </c>
-      <c r="B64" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B64" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C64" s="3" t="n">
         <v>0</v>
@@ -2538,19 +2482,19 @@
         <v>0</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>0</v>
+        <v>0.001563</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>0</v>
+        <v>0.262095</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>0</v>
+        <v>1.20844</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>0</v>
+        <v>1.347884</v>
       </c>
       <c r="I64" s="3" t="n">
-        <v>0</v>
+        <v>1.500303</v>
       </c>
     </row>
     <row r="65">
@@ -2559,10 +2503,8 @@
           <t xml:space="preserve">    Total Tax Payable</t>
         </is>
       </c>
-      <c r="B65" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B65" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C65" s="3" t="n">
         <v>0</v>
@@ -2592,10 +2534,8 @@
           <t xml:space="preserve">    Other Current Payables</t>
         </is>
       </c>
-      <c r="B66" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B66" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C66" s="3" t="n">
         <v>0</v>
@@ -2625,10 +2565,8 @@
           <t xml:space="preserve">    Current Accrued Expense</t>
         </is>
       </c>
-      <c r="B67" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B67" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C67" s="3" t="n">
         <v>0</v>
@@ -2646,10 +2584,10 @@
         <v>0</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>0</v>
+        <v>0.112875</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>0</v>
+        <v>0.236293</v>
       </c>
     </row>
     <row r="68">
@@ -2658,10 +2596,8 @@
           <t xml:space="preserve">  Accounts Payable &amp; Accrued Expense</t>
         </is>
       </c>
-      <c r="B68" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B68" s="3" t="n">
+        <v>0.003036</v>
       </c>
       <c r="C68" s="3" t="n">
         <v>0.003076</v>
@@ -2691,10 +2627,8 @@
           <t xml:space="preserve">    Short-Term Debt</t>
         </is>
       </c>
-      <c r="B69" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B69" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C69" s="3" t="n">
         <v>0</v>
@@ -2724,10 +2658,8 @@
           <t xml:space="preserve">    Short-Term Capital Lease Obligation</t>
         </is>
       </c>
-      <c r="B70" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B70" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C70" s="3" t="n">
         <v>0</v>
@@ -2757,10 +2689,8 @@
           <t xml:space="preserve">  Short-Term Debt &amp; Capital Lease Obligation</t>
         </is>
       </c>
-      <c r="B71" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B71" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C71" s="3" t="n">
         <v>0</v>
@@ -2790,10 +2720,8 @@
           <t xml:space="preserve">    Current Deferred Revenue</t>
         </is>
       </c>
-      <c r="B72" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B72" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C72" s="3" t="n">
         <v>0</v>
@@ -2823,10 +2751,8 @@
           <t xml:space="preserve">    Current Deferred Taxes Liabilities</t>
         </is>
       </c>
-      <c r="B73" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B73" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C73" s="3" t="n">
         <v>0</v>
@@ -2856,10 +2782,8 @@
           <t xml:space="preserve">  Deferred Tax And Revenue</t>
         </is>
       </c>
-      <c r="B74" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B74" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C74" s="3" t="n">
         <v>0</v>
@@ -2889,10 +2813,8 @@
           <t xml:space="preserve">  Other Current Liabilities</t>
         </is>
       </c>
-      <c r="B75" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B75" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C75" s="3" t="n">
         <v>0</v>
@@ -2922,10 +2844,8 @@
           <t xml:space="preserve">  Total Current Liabilities</t>
         </is>
       </c>
-      <c r="B76" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B76" s="3" t="n">
+        <v>0.003036</v>
       </c>
       <c r="C76" s="3" t="n">
         <v>0.003076</v>
@@ -2955,10 +2875,8 @@
           <t xml:space="preserve">    Long-Term Debt</t>
         </is>
       </c>
-      <c r="B77" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B77" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C77" s="3" t="n">
         <v>0</v>
@@ -2988,10 +2906,8 @@
           <t xml:space="preserve">    Long-Term Capital Lease Obligation</t>
         </is>
       </c>
-      <c r="B78" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B78" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C78" s="3" t="n">
         <v>0</v>
@@ -3021,10 +2937,8 @@
           <t xml:space="preserve">  Long-Term Debt &amp; Capital Lease Obligation</t>
         </is>
       </c>
-      <c r="B79" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B79" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C79" s="3" t="n">
         <v>0</v>
@@ -3101,10 +3015,8 @@
           <t xml:space="preserve">  Pension And Retirement Benefit</t>
         </is>
       </c>
-      <c r="B81" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B81" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C81" s="3" t="n">
         <v>0</v>
@@ -3134,10 +3046,8 @@
           <t xml:space="preserve">    NonCurrent Deferred Revenue</t>
         </is>
       </c>
-      <c r="B82" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B82" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C82" s="3" t="n">
         <v>0</v>
@@ -3167,10 +3077,8 @@
           <t xml:space="preserve">  NonCurrent Deferred Liabilities</t>
         </is>
       </c>
-      <c r="B83" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B83" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C83" s="3" t="n">
         <v>0</v>
@@ -3200,10 +3108,8 @@
           <t xml:space="preserve">  NonCurrent Deferred Income Tax</t>
         </is>
       </c>
-      <c r="B84" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B84" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C84" s="3" t="n">
         <v>0</v>
@@ -3233,10 +3139,8 @@
           <t xml:space="preserve">  Other Long-Term Liabilities</t>
         </is>
       </c>
-      <c r="B85" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B85" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C85" s="3" t="n">
         <v>0</v>
@@ -3336,10 +3240,8 @@
           <t xml:space="preserve">  Common Stock</t>
         </is>
       </c>
-      <c r="B88" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B88" s="3" t="n">
+        <v>0.431395</v>
       </c>
       <c r="C88" s="3" t="n">
         <v>0.431395</v>
@@ -3369,10 +3271,8 @@
           <t xml:space="preserve">  Preferred Stock</t>
         </is>
       </c>
-      <c r="B89" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B89" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C89" s="3" t="n">
         <v>0</v>
@@ -3402,10 +3302,8 @@
           <t xml:space="preserve">  Retained Earnings</t>
         </is>
       </c>
-      <c r="B90" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B90" s="3" t="n">
+        <v>-0.1086</v>
       </c>
       <c r="C90" s="3" t="n">
         <v>-0.09804400000000001</v>
@@ -3435,10 +3333,8 @@
           <t xml:space="preserve">  Accumulated other comprehensive income (loss)</t>
         </is>
       </c>
-      <c r="B91" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B91" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C91" s="3" t="n">
         <v>0</v>
@@ -3468,10 +3364,8 @@
           <t xml:space="preserve">  Additional Paid-In Capital</t>
         </is>
       </c>
-      <c r="B92" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B92" s="3" t="n">
+        <v>0.08080900000000001</v>
       </c>
       <c r="C92" s="3" t="n">
         <v>0.08080900000000001</v>
@@ -3501,10 +3395,8 @@
           <t xml:space="preserve">  Treasury Stock</t>
         </is>
       </c>
-      <c r="B93" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B93" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C93" s="3" t="n">
         <v>0</v>
@@ -3534,10 +3426,8 @@
           <t xml:space="preserve">  Total Stockholders Equity</t>
         </is>
       </c>
-      <c r="B94" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B94" s="3" t="n">
+        <v>0.403604</v>
       </c>
       <c r="C94" s="3" t="n">
         <v>0.41416</v>
@@ -3567,10 +3457,8 @@
           <t xml:space="preserve">  Minority Interest</t>
         </is>
       </c>
-      <c r="B95" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B95" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C95" s="3" t="n">
         <v>0</v>
@@ -3600,10 +3488,8 @@
           <t>Total Equity</t>
         </is>
       </c>
-      <c r="B96" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B96" s="3" t="n">
+        <v>0.403604</v>
       </c>
       <c r="C96" s="3" t="n">
         <v>0.41416</v>
@@ -3756,10 +3642,10 @@
         <v>0</v>
       </c>
       <c r="H101" s="3" t="n">
-        <v>0</v>
+        <v>0.004236</v>
       </c>
       <c r="I101" s="3" t="n">
-        <v>0</v>
+        <v>0.09837600000000001</v>
       </c>
     </row>
     <row r="102">
@@ -3911,10 +3797,10 @@
         <v>0.904515</v>
       </c>
       <c r="H106" s="3" t="n">
-        <v>0.180627</v>
+        <v>0.184863</v>
       </c>
       <c r="I106" s="3" t="n">
-        <v>0.415143</v>
+        <v>0.5135189999999999</v>
       </c>
     </row>
     <row r="107">
@@ -5161,10 +5047,8 @@
           <t>CurrentAssets</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E6" s="5" t="n">
+        <v>0.40664</v>
       </c>
       <c r="F6" s="5" t="n">
         <v>0.417236</v>
@@ -5375,10 +5259,8 @@
           <t>CurrentLiabilities</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E10" s="5" t="n">
+        <v>0.003036</v>
       </c>
       <c r="F10" s="5" t="n">
         <v>0.003076</v>
@@ -7135,15 +7017,11 @@
           <t>CashAndCashEquivalents</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E41" s="5" t="n">
+        <v>0.007087</v>
+      </c>
+      <c r="F41" s="5" t="n">
+        <v>0.006232</v>
       </c>
       <c r="G41" s="5" t="n">
         <v>0.22481</v>
@@ -7823,21 +7701,19 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Cash and cash equivalents $</t>
+          <t>Accrued interest receivable</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>CashAndCashEquivalents</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>AccruedInterestReceivable</t>
+        </is>
+      </c>
+      <c r="E53" s="5" t="n">
+        <v>0.000553</v>
       </c>
       <c r="F53" s="5" t="n">
-        <v>0.006232</v>
+        <v>0.002004</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -7883,21 +7759,19 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Accrued interest receivable</t>
+          <t>Short-term investment (note 4)</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>AccruedInterestReceivable</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>ShortTermInvestments</t>
+        </is>
+      </c>
+      <c r="E54" s="5" t="n">
+        <v>0.399</v>
       </c>
       <c r="F54" s="5" t="n">
-        <v>0.002004</v>
+        <v>0.409</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -7938,26 +7812,24 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Current assets</t>
+          <t>Current liabilities</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Short-term investment (note 4)</t>
+          <t>Accounts payable and accrued liabilities $</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>ShortTermInvestments</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>PayablesAndAccruedExpenses</t>
+        </is>
+      </c>
+      <c r="E55" s="5" t="n">
+        <v>0.003036</v>
       </c>
       <c r="F55" s="5" t="n">
-        <v>0.409</v>
+        <v>0.003076</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -7998,26 +7870,24 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Current liabilities</t>
+          <t>SHAREHOLDERS' EQUITY</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Accounts payable and accrued liabilities $</t>
+          <t>Share capital (note 5)</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>PayablesAndAccruedExpenses</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>CapitalStock</t>
+        </is>
+      </c>
+      <c r="E56" s="5" t="n">
+        <v>0.431395</v>
       </c>
       <c r="F56" s="5" t="n">
-        <v>0.003076</v>
+        <v>0.431395</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
@@ -8063,21 +7933,19 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Share capital (note 5)</t>
+          <t>Reserves (note 5)</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>CapitalStock</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
+      <c r="E57" s="5" t="n">
+        <v>0.08080900000000001</v>
       </c>
       <c r="F57" s="5" t="n">
-        <v>0.431395</v>
+        <v>0.08080900000000001</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -8123,21 +7991,19 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Reserves (note 5)</t>
+          <t>Deficit</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>AdditionalPaidInCapital</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>RetainedEarnings</t>
+        </is>
+      </c>
+      <c r="E58" s="5" t="n">
+        <v>-0.1086</v>
       </c>
       <c r="F58" s="5" t="n">
-        <v>0.08080900000000001</v>
+        <v>-0.09804400000000001</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -8183,21 +8049,19 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Deficit</t>
+          <t>SHAREHOLDERS' EQUITY total</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>RetainedEarnings</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>StockholdersEquity</t>
+        </is>
+      </c>
+      <c r="E59" s="5" t="n">
+        <v>0.403604</v>
       </c>
       <c r="F59" s="5" t="n">
-        <v>-0.09804400000000001</v>
+        <v>0.41416</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -8238,17 +8102,17 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>SHAREHOLDERS' EQUITY</t>
+          <t>Current assets</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>SHAREHOLDERS' EQUITY total</t>
+          <t>Cash and cash equivalents $</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>StockholdersEquity</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -8257,7 +8121,7 @@
         </is>
       </c>
       <c r="F60" s="5" t="n">
-        <v>0.41416</v>
+        <v>0.006232</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
@@ -8528,7 +8392,11 @@
           <t>Write-off of GST receivable</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr"/>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E65" t="inlineStr">
         <is>
           <t>-</t>
@@ -8692,7 +8560,11 @@
           <t>GST receivable</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr"/>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E68" t="inlineStr">
         <is>
           <t>-</t>
@@ -8976,7 +8848,11 @@
           <t>Proceeds from private placement</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr"/>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E73" t="inlineStr">
         <is>
           <t>-</t>
@@ -10054,7 +9930,11 @@
           <t>Private placement (Note 6) 8,150,000 988,750 30,000</t>
         </is>
       </c>
-      <c r="D92" t="inlineStr"/>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E92" t="inlineStr">
         <is>
           <t>-</t>
